--- a/imports/Metodologia.xlsx
+++ b/imports/Metodologia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B2D063-B779-4F75-B17F-AC01DDAD2ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B866B7-5F21-40F3-A7D4-151ED0782980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="2" xr2:uid="{5C5D13DF-E461-4B29-A220-9E515729D54F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="182">
   <si>
     <t>BD</t>
   </si>
@@ -247,24 +247,6 @@
     <t>Cambiar la funda de microfibra cuando este visiblemente sucia o llena de polvo.</t>
   </si>
   <si>
-    <t>Vidrios altos: Aplique el químico uniformemente sobre el mop de vidrios (TM-VI-02) y ajuste bastón retractil de acuerdo a la altura requerida.</t>
-  </si>
-  <si>
-    <t>Coloque el mop de vidrios en el área a limpiar, asegurando contacto completo con el vidrio, manteniendo presión ligera y uniforme.</t>
-  </si>
-  <si>
-    <t>Comenzar a limpiar de arriba hacia abajo y de izquierda a derecha hasta cubrir completamente la superficie alcanzable.</t>
-  </si>
-  <si>
-    <t>Vidrios medios e inferiores: Aplique el químico directamente sobre la microfibra y prepare el paño utilizando la técnica de 8 caras (TM-SA-001).</t>
-  </si>
-  <si>
-    <t>Limpie el vidrio de arriba hacia abajo y de izquierda a derecha utilizando la técnica (TM-VI-001) una cara húmeda de la microfibra; cambiar cara cuando esté sucia.</t>
-  </si>
-  <si>
-    <t>Revise el vidrio contra la luz y corrija irregularidades utilizando la técnica de 8 caras (TM-SA-001).</t>
-  </si>
-  <si>
     <t>No mueva muebles ni objetos; solo se barrerán las áreas visibles.</t>
   </si>
   <si>
@@ -551,6 +533,57 @@
   </si>
   <si>
     <t>Con una cara húmeda del paño, limpie la superficie asignada, incluyendo las zonas de difícil acceso u ocultas. Limpie también los objetos autorizados retirados</t>
+  </si>
+  <si>
+    <t>Aplique el químico uniformemente sobre el mop de vidrios y ajuste el bastón retráctil de acuerdo a la altura requerida.</t>
+  </si>
+  <si>
+    <t>Coloque el mop de vidrios en el área a limpiar, asegurando contacto completo con el vidrio.</t>
+  </si>
+  <si>
+    <t>Comience a limpiar de arriba hacia abajo y de izquierda a derecha utilizando la técnica (TM-VI-001) hasta cubrir completamente la superficie alcanzable.</t>
+  </si>
+  <si>
+    <t>Revise el vidrio contra la luz y corrija irregularidades repitiendo el pase en la zona afectada hasta eliminar marcas o residuos.</t>
+  </si>
+  <si>
+    <t>ACOMODAR</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>MB-AC-001</t>
+  </si>
+  <si>
+    <t>Acomodar Trastes</t>
+  </si>
+  <si>
+    <t>FR-AC-001</t>
+  </si>
+  <si>
+    <t>Verifique que los trastes colocados en el escurridor estén completamente secos.</t>
+  </si>
+  <si>
+    <t>Retire las tazas y utensilios secos del escurridor y colóquelos en su lugar correspondiente.</t>
+  </si>
+  <si>
+    <t>FR-TA-001</t>
+  </si>
+  <si>
+    <t>Lavar Trastes</t>
+  </si>
+  <si>
+    <t>MB-TA-001</t>
+  </si>
+  <si>
+    <t>Prepare la solución de lavado en un contenedor y lave cada traste por separado con la esponja.</t>
+  </si>
+  <si>
+    <t>Enjuague los trastes con agua limpia y colóquelos en el escurridor para que sequen.</t>
+  </si>
+  <si>
+    <t>Limpie la tarja de la cocina con el paño de microfibra asignado, retire los residuos del colador y deje la tarja seca.</t>
   </si>
 </sst>
 </file>
@@ -650,7 +683,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -698,12 +731,8 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -711,19 +740,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -732,7 +748,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -789,13 +805,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -816,11 +826,70 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1213,14 +1282,14 @@
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="G1" s="20" t="s">
+      <c r="E1" s="21"/>
+      <c r="G1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="21"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -1233,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>1</v>
@@ -1256,10 +1325,10 @@
         <v>25</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>13</v>
@@ -1273,16 +1342,16 @@
         <v>48</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>15</v>
@@ -1296,16 +1365,16 @@
         <v>49</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>17</v>
@@ -1319,16 +1388,16 @@
         <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>19</v>
@@ -1342,7 +1411,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>23</v>
@@ -1351,7 +1420,7 @@
         <v>52</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>21</v>
@@ -1365,7 +1434,7 @@
         <v>53</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>15</v>
@@ -1374,7 +1443,7 @@
         <v>54</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>23</v>
@@ -1388,7 +1457,7 @@
         <v>55</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>15</v>
@@ -1397,7 +1466,7 @@
         <v>54</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>25</v>
@@ -1411,7 +1480,7 @@
         <v>56</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>15</v>
@@ -1420,7 +1489,7 @@
         <v>54</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>26</v>
@@ -1431,19 +1500,19 @@
     </row>
     <row r="11" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>33</v>
@@ -1454,183 +1523,224 @@
     </row>
     <row r="12" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I16" s="10"/>
     </row>
     <row r="17" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="22" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
     <row r="23" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="24" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="25" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H3:H8 H10">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H8">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1638,35 +1748,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713EC40E-CFCC-4E88-8410-5E71B8B4F27E}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L1048576"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="18.59765625" customWidth="1"/>
-    <col min="7" max="7" width="12.86328125" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" customWidth="1"/>
     <col min="8" max="8" width="8.73046875" customWidth="1"/>
     <col min="9" max="9" width="14.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="24" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
       <c r="G1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="21"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -1682,7 +1792,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>
@@ -1709,16 +1819,16 @@
         <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>13</v>
@@ -1739,16 +1849,16 @@
         <v>46</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>15</v>
@@ -1769,16 +1879,16 @@
         <v>46</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>17</v>
@@ -1799,16 +1909,16 @@
         <v>48</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>19</v>
@@ -1829,16 +1939,16 @@
         <v>48</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>21</v>
@@ -1859,16 +1969,16 @@
         <v>49</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
@@ -1889,16 +1999,16 @@
         <v>50</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F9" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>25</v>
@@ -1910,7 +2020,7 @@
     </row>
     <row r="10" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B10" s="5">
         <v>3</v>
@@ -1919,13 +2029,13 @@
         <v>51</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>52</v>
@@ -1940,7 +2050,7 @@
     </row>
     <row r="11" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
@@ -1949,13 +2059,13 @@
         <v>53</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>54</v>
@@ -1970,7 +2080,7 @@
     </row>
     <row r="12" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B12" s="5">
         <v>2</v>
@@ -1979,28 +2089,28 @@
         <v>55</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>54</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B13" s="5">
         <v>3</v>
@@ -2009,353 +2119,470 @@
         <v>56</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>54</v>
       </c>
       <c r="H13" s="4"/>
+      <c r="I13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B14" s="5">
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B15" s="5">
         <v>2</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B16" s="5">
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B17" s="5">
         <v>1</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B18" s="5">
         <v>2</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B19" s="5">
         <v>3</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B21" s="5">
         <v>2</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B22" s="5">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B23" s="5">
         <v>1</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B24" s="5">
         <v>2</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B25" s="5">
         <v>3</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="A26" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="A27" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="A28" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" s="5">
+        <v>3</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="A29" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" s="5">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="A30" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" s="28">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="28">
+        <v>3</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="33" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="34" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="35" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="36" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="37" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="38" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="39" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="40" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="41" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="42" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="43" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1048576" spans="6:6" x14ac:dyDescent="0.45">
+      <c r="F1048576" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2379,7 +2606,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA2C063-C098-4059-B8EE-5F5C8D6DB356}">
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.265625" customWidth="1"/>
@@ -2392,24 +2619,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="26" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
       <c r="G1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="4"/>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="21"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:14" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2431,7 +2658,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="8" t="s">
@@ -2452,13 +2679,13 @@
         <v>59</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>57</v>
@@ -2482,13 +2709,13 @@
         <v>60</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>57</v>
@@ -2512,13 +2739,13 @@
         <v>61</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>57</v>
@@ -2542,13 +2769,13 @@
         <v>62</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>57</v>
@@ -2572,13 +2799,13 @@
         <v>63</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>58</v>
@@ -2604,13 +2831,13 @@
         <v>64</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>58</v>
@@ -2636,13 +2863,13 @@
         <v>65</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>58</v>
@@ -2668,13 +2895,13 @@
         <v>28</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -2698,13 +2925,13 @@
         <v>66</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>39</v>
@@ -2728,23 +2955,23 @@
         <v>30</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>39</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
@@ -2758,18 +2985,24 @@
         <v>31</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>39</v>
       </c>
       <c r="H13" s="4"/>
+      <c r="I13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
@@ -2782,13 +3015,13 @@
         <v>29</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>39</v>
@@ -2806,13 +3039,13 @@
         <v>67</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>39</v>
@@ -2830,13 +3063,13 @@
         <v>34</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>39</v>
@@ -2854,13 +3087,13 @@
         <v>35</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>39</v>
@@ -2878,13 +3111,13 @@
         <v>68</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>39</v>
@@ -2898,17 +3131,17 @@
       <c r="B19" s="5">
         <v>1</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>69</v>
+      <c r="C19" s="16" t="s">
+        <v>165</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>39</v>
@@ -2923,16 +3156,16 @@
         <v>2</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>39</v>
@@ -2947,16 +3180,16 @@
         <v>3</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>39</v>
@@ -2971,16 +3204,16 @@
         <v>4</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>39</v>
@@ -2990,49 +3223,49 @@
     </row>
     <row r="23" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H24" s="4"/>
     </row>
@@ -3041,19 +3274,19 @@
         <v>53</v>
       </c>
       <c r="B25" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>37</v>
@@ -3062,49 +3295,49 @@
     </row>
     <row r="26" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B27" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H27" s="4"/>
     </row>
@@ -3113,19 +3346,19 @@
         <v>55</v>
       </c>
       <c r="B28" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>38</v>
@@ -3137,19 +3370,19 @@
         <v>55</v>
       </c>
       <c r="B29" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>38</v>
@@ -3158,49 +3391,49 @@
     </row>
     <row r="30" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B30" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H31" s="4"/>
     </row>
@@ -3209,19 +3442,19 @@
         <v>56</v>
       </c>
       <c r="B32" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>39</v>
@@ -3233,19 +3466,19 @@
         <v>56</v>
       </c>
       <c r="B33" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>39</v>
@@ -3254,70 +3487,70 @@
     </row>
     <row r="34" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="5" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B34" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="5" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B35" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B36" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>37</v>
@@ -3326,22 +3559,22 @@
     </row>
     <row r="37" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B37" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>37</v>
@@ -3350,70 +3583,70 @@
     </row>
     <row r="38" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B38" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>37</v>
+        <v>133</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B39" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>37</v>
+        <v>133</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B40" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>38</v>
@@ -3422,22 +3655,22 @@
     </row>
     <row r="41" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B41" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>38</v>
@@ -3446,22 +3679,22 @@
     </row>
     <row r="42" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B42" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>38</v>
@@ -3470,70 +3703,70 @@
     </row>
     <row r="43" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B43" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>38</v>
+        <v>133</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B44" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>38</v>
+        <v>133</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B45" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>39</v>
@@ -3542,22 +3775,22 @@
     </row>
     <row r="46" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B46" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>39</v>
@@ -3566,22 +3799,22 @@
     </row>
     <row r="47" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B47" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>39</v>
@@ -3590,70 +3823,70 @@
     </row>
     <row r="48" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B48" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>20</v>
+        <v>132</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>39</v>
+        <v>133</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="H48" s="16"/>
     </row>
     <row r="49" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B49" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>20</v>
+        <v>132</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>39</v>
+        <v>133</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B50" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>37</v>
@@ -3662,22 +3895,22 @@
     </row>
     <row r="51" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B51" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>37</v>
@@ -3686,22 +3919,22 @@
     </row>
     <row r="52" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B52" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>37</v>
@@ -3710,70 +3943,70 @@
     </row>
     <row r="53" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B53" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B54" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H54" s="16"/>
     </row>
     <row r="55" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B55" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>38</v>
@@ -3782,22 +4015,22 @@
     </row>
     <row r="56" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B56" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>38</v>
@@ -3806,22 +4039,22 @@
     </row>
     <row r="57" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B57" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>38</v>
@@ -3830,70 +4063,70 @@
     </row>
     <row r="58" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B58" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B59" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H59" s="12"/>
     </row>
     <row r="60" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B60" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>39</v>
@@ -3905,22 +4138,22 @@
     </row>
     <row r="61" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B61" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>39</v>
@@ -3932,22 +4165,22 @@
     </row>
     <row r="62" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B62" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>39</v>
@@ -3959,22 +4192,22 @@
     </row>
     <row r="63" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B63" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>39</v>
@@ -3986,22 +4219,22 @@
     </row>
     <row r="64" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B64" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>39</v>
@@ -4016,22 +4249,22 @@
         <v>103</v>
       </c>
       <c r="B65" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>39</v>
+        <v>133</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
@@ -4043,22 +4276,22 @@
         <v>103</v>
       </c>
       <c r="B66" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>39</v>
+        <v>133</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="H66" s="12"/>
       <c r="I66" s="12"/>
@@ -4067,22 +4300,22 @@
     </row>
     <row r="67" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B67" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>57</v>
@@ -4091,22 +4324,22 @@
     </row>
     <row r="68" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B68" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>57</v>
@@ -4115,22 +4348,22 @@
     </row>
     <row r="69" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B69" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>57</v>
@@ -4142,22 +4375,22 @@
     </row>
     <row r="70" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B70" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>57</v>
@@ -4169,25 +4402,25 @@
     </row>
     <row r="71" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="5" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="B71" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>87</v>
+        <v>132</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>57</v>
+        <v>133</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
@@ -4196,25 +4429,25 @@
     </row>
     <row r="72" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="5" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="B72" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>87</v>
+        <v>132</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>57</v>
+        <v>133</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
@@ -4223,22 +4456,22 @@
     </row>
     <row r="73" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B73" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>37</v>
@@ -4250,25 +4483,25 @@
     </row>
     <row r="74" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B74" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
@@ -4277,25 +4510,25 @@
     </row>
     <row r="75" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B75" s="5">
-        <v>3</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>162</v>
+        <v>2</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
@@ -4304,22 +4537,22 @@
     </row>
     <row r="76" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B76" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>38</v>
@@ -4327,68 +4560,68 @@
     </row>
     <row r="77" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B77" s="5">
-        <v>2</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>169</v>
+        <v>1</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>38</v>
+        <v>133</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B78" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>38</v>
+        <v>133</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B79" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>39</v>
@@ -4396,81 +4629,156 @@
     </row>
     <row r="80" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B80" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A81" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B81" s="5">
+    <row r="81" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B81" s="28">
+        <v>1</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E81" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="F81" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G81" s="28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" s="28">
+        <v>2</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D82" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E82" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="F82" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G82" s="28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B83" s="28">
+        <v>1</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D83" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E83" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F83" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G83" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="I83" s="33"/>
+      <c r="J83" s="31"/>
+      <c r="K83" s="31"/>
+      <c r="L83" s="31"/>
+      <c r="M83" s="31"/>
+      <c r="N83" s="31"/>
+      <c r="O83" s="31"/>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="32"/>
+    </row>
+    <row r="84" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B84" s="28">
+        <v>2</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D84" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E84" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F84" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G84" s="28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B85" s="28">
         <v>3</v>
       </c>
-      <c r="C81" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B82" s="5">
-        <v>4</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="84" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="85" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="86" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="87" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="88" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="89" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="90" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+      <c r="C85" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D85" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E85" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F85" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G85" s="28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="87" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="88" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="89" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="90" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>

--- a/imports/Metodologia.xlsx
+++ b/imports/Metodologia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B866B7-5F21-40F3-A7D4-151ED0782980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D948D432-641D-486F-98A2-AA4DF98D0EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="2" xr2:uid="{5C5D13DF-E461-4B29-A220-9E515729D54F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{5C5D13DF-E461-4B29-A220-9E515729D54F}"/>
   </bookViews>
   <sheets>
     <sheet name="MetodologiaBase" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="194">
   <si>
     <t>BD</t>
   </si>
@@ -584,6 +584,42 @@
   </si>
   <si>
     <t>Limpie la tarja de la cocina con el paño de microfibra asignado, retire los residuos del colador y deje la tarja seca.</t>
+  </si>
+  <si>
+    <t>MB-MS-001</t>
+  </si>
+  <si>
+    <t>Mop Seco</t>
+  </si>
+  <si>
+    <t>MOP</t>
+  </si>
+  <si>
+    <t>Mop Humedo</t>
+  </si>
+  <si>
+    <t>MB-MH-001</t>
+  </si>
+  <si>
+    <t>FR-MH-001</t>
+  </si>
+  <si>
+    <t>MH</t>
+  </si>
+  <si>
+    <t>Rocía el químico asignado al área (ya diluido) por secciones pequeñas, sin hacer charcos.</t>
+  </si>
+  <si>
+    <t>Revisa el piso antes de empezar y si ves papel o tierra, levántalo primero con el recogedor o una toalla para no arrastrarlo.</t>
+  </si>
+  <si>
+    <t>Pasa la mopa asignada al área en líneas rectas avanzando hacia la salida y sin regresar sobre lo ya limpio.</t>
+  </si>
+  <si>
+    <t>Si al final del recorrido quedó algún sólido, no lo empujes con la mopa, recógelo con el cepillo y el recogedor y luego da un pase rápido solo en esa zona.</t>
+  </si>
+  <si>
+    <t>Si la mopa se ve sucia o deja marcas, cámbiala por una limpia</t>
   </si>
 </sst>
 </file>
@@ -748,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -802,6 +838,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -809,6 +851,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -826,65 +871,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1277,19 +1274,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="G1" s="27" t="s">
+      <c r="E1" s="23"/>
+      <c r="G1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="27"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -1688,10 +1685,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="5" t="s">
         <v>172</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -1708,10 +1705,10 @@
       <c r="A22" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -1721,8 +1718,28 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="24" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="23" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>184</v>
+      </c>
+    </row>
     <row r="25" spans="1:5" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="3">
@@ -1730,17 +1747,17 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
+  <conditionalFormatting sqref="H3:H8">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H10">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H8">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1748,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713EC40E-CFCC-4E88-8410-5E71B8B4F27E}">
-  <dimension ref="A1:L1048576"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
@@ -1760,23 +1777,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="22" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
       <c r="G1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="27"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2433,7 +2450,7 @@
       <c r="B26" s="5">
         <v>1</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -2457,7 +2474,7 @@
       <c r="B27" s="5">
         <v>2</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -2481,7 +2498,7 @@
       <c r="B28" s="5">
         <v>3</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -2526,7 +2543,7 @@
       <c r="A30" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="5">
         <v>2</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -2550,7 +2567,7 @@
       <c r="A31" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="5">
         <v>3</v>
       </c>
       <c r="C31" s="5" t="s">
@@ -2569,21 +2586,84 @@
         <v>177</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="33" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="34" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="35" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="36" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="37" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="38" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="39" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="40" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="41" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="42" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="43" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="1048576" spans="6:6" x14ac:dyDescent="0.45">
-      <c r="F1048576" s="34"/>
-    </row>
+    <row r="32" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="30">
+        <v>1</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G32" s="30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="30">
+        <v>2</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" s="30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B34" s="30">
+        <v>3</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="36" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="37" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="38" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="39" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="40" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="42" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="43" spans="1:7" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
@@ -2619,24 +2699,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="24" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
       <c r="G1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="4"/>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="27"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:14" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -4651,48 +4731,48 @@
       </c>
     </row>
     <row r="81" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A81" s="28" t="s">
+      <c r="A81" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B81" s="28">
+      <c r="B81" s="5">
         <v>1</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D81" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E81" s="28" t="s">
+      <c r="D81" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F81" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G81" s="28" t="s">
+      <c r="F81" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G81" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="82" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="28" t="s">
+      <c r="A82" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B82" s="28">
+      <c r="B82" s="5">
         <v>2</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D82" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E82" s="28" t="s">
+      <c r="D82" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E82" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F82" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G82" s="28" t="s">
+      <c r="F82" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G82" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4700,54 +4780,54 @@
       <c r="A83" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B83" s="28">
+      <c r="B83" s="5">
         <v>1</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D83" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E83" s="28" t="s">
+      <c r="D83" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G83" s="28" t="s">
+      <c r="F83" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G83" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I83" s="33"/>
-      <c r="J83" s="31"/>
-      <c r="K83" s="31"/>
-      <c r="L83" s="31"/>
-      <c r="M83" s="31"/>
-      <c r="N83" s="31"/>
-      <c r="O83" s="31"/>
-      <c r="P83" s="31"/>
-      <c r="Q83" s="32"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="19"/>
+      <c r="K83" s="19"/>
+      <c r="L83" s="19"/>
+      <c r="M83" s="19"/>
+      <c r="N83" s="19"/>
+      <c r="O83" s="19"/>
+      <c r="P83" s="19"/>
+      <c r="Q83" s="20"/>
     </row>
     <row r="84" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B84" s="28">
+      <c r="B84" s="5">
         <v>2</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D84" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E84" s="28" t="s">
+      <c r="D84" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E84" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F84" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G84" s="28" t="s">
+      <c r="F84" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G84" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4755,30 +4835,140 @@
       <c r="A85" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B85" s="28">
+      <c r="B85" s="5">
         <v>3</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D85" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E85" s="28" t="s">
+      <c r="D85" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E85" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F85" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G85" s="28" t="s">
+      <c r="F85" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G85" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="87" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="88" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="89" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="90" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="86" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B86" s="30">
+        <v>1</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F86" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B87" s="30">
+        <v>2</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F87" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" s="30">
+        <v>3</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F88" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B89" s="30">
+        <v>4</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F89" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B90" s="30">
+        <v>5</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F90" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
